--- a/AAII_Financials/Quarterly/ANVS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANVS_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/ANVS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANVS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
   <si>
     <t>ANVS</t>
   </si>
@@ -656,122 +656,129 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -847,8 +854,14 @@
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -924,8 +937,14 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1001,8 +1020,14 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1030,85 +1055,93 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E12" s="3">
+        <v>8900</v>
+      </c>
+      <c r="F12" s="3">
         <v>13800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>8300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>7800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>1600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>4100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>4000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>2100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>2900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>1400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>2400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>1400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>800</v>
       </c>
-      <c r="T12" s="3">
-        <v>0</v>
-      </c>
-      <c r="U12" s="3">
-        <v>0</v>
-      </c>
       <c r="V12" s="3">
         <v>0</v>
       </c>
       <c r="W12" s="3">
+        <v>0</v>
+      </c>
+      <c r="X12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
         <v>200</v>
       </c>
-      <c r="X12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>0</v>
-      </c>
       <c r="Z12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="3">
         <v>100</v>
       </c>
-      <c r="AA12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,8 +1217,14 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1198,11 +1237,11 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
@@ -1223,26 +1262,26 @@
         <v>0</v>
       </c>
       <c r="O14" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="P14" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="3">
         <v>-200</v>
       </c>
       <c r="R14" s="3">
+        <v>-600</v>
+      </c>
+      <c r="S14" s="3">
         <v>-200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U14" s="3">
         <v>-700</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1252,17 +1291,23 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1338,8 +1383,14 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,85 +1415,93 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>10400</v>
+      </c>
+      <c r="F17" s="3">
         <v>14900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>9800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>10000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>3200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>6500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>6000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>5300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>5900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>3200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>100</v>
-      </c>
-      <c r="T17" s="3">
-        <v>200</v>
-      </c>
-      <c r="U17" s="3">
-        <v>300</v>
       </c>
       <c r="V17" s="3">
         <v>200</v>
       </c>
       <c r="W17" s="3">
+        <v>300</v>
+      </c>
+      <c r="X17" s="3">
         <v>200</v>
-      </c>
-      <c r="X17" s="3">
-        <v>100</v>
       </c>
       <c r="Y17" s="3">
         <v>200</v>
       </c>
       <c r="Z17" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA17" s="3">
         <v>200</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1450,76 +1509,82 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="G18" s="3">
         <v>-9800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-10000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-3200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-6500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-6000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-5300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-5900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-2900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-2500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-3200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-1700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-2300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-100</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-300</v>
       </c>
       <c r="V18" s="3">
         <v>-200</v>
       </c>
       <c r="W18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="X18" s="3">
         <v>-200</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-100</v>
       </c>
       <c r="Y18" s="3">
         <v>-200</v>
       </c>
       <c r="Z18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-200</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,8 +1612,10 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1556,23 +1623,23 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="F20" s="3">
+        <v>100</v>
+      </c>
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
@@ -1598,14 +1665,14 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
@@ -1621,19 +1688,25 @@
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
+      <c r="E21" s="3">
+        <v>-22200</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>3</v>
@@ -1701,8 +1774,14 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1778,85 +1857,97 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-22200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-14700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-9500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-9700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-3100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-6400</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-5200</v>
       </c>
       <c r="K23" s="3">
         <v>-5900</v>
       </c>
       <c r="L23" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="M23" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="N23" s="3">
         <v>-2800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-2500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-3200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-1700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-2300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-200</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-200</v>
-      </c>
-      <c r="X23" s="3">
-        <v>-100</v>
       </c>
       <c r="Y23" s="3">
         <v>-200</v>
       </c>
       <c r="Z23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-200</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1932,8 +2023,14 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,162 +2106,180 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-22200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-14700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-9500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-9700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-3100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-6400</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-5200</v>
       </c>
       <c r="K26" s="3">
         <v>-5900</v>
       </c>
       <c r="L26" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="M26" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="N26" s="3">
         <v>-2800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-2500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-3200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-1700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-2300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-200</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="X26" s="3">
-        <v>-100</v>
       </c>
       <c r="Y26" s="3">
         <v>-200</v>
       </c>
       <c r="Z26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-200</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-22200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-14700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-9500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-9700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-3100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-6400</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-5200</v>
       </c>
       <c r="K27" s="3">
         <v>-5900</v>
       </c>
       <c r="L27" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="M27" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="N27" s="3">
         <v>-2800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-2500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-3200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-1700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-2300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-200</v>
-      </c>
-      <c r="W27" s="3">
-        <v>-200</v>
-      </c>
-      <c r="X27" s="3">
-        <v>-100</v>
       </c>
       <c r="Y27" s="3">
         <v>-200</v>
       </c>
       <c r="Z27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-200</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2355,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2317,8 +2438,14 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2521,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,8 +2604,14 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2480,23 +2619,23 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
@@ -2522,14 +2661,14 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
@@ -2545,88 +2684,100 @@
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-22200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-14700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-9500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-9700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-3100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-6400</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-5200</v>
       </c>
       <c r="K33" s="3">
         <v>-5900</v>
       </c>
       <c r="L33" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="M33" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="N33" s="3">
         <v>-2800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-2500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-3200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-1700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-2300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-200</v>
-      </c>
-      <c r="W33" s="3">
-        <v>-200</v>
-      </c>
-      <c r="X33" s="3">
-        <v>-100</v>
       </c>
       <c r="Y33" s="3">
         <v>-200</v>
       </c>
       <c r="Z33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-200</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,167 +2853,185 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-22200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-14700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-9500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-9700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-3100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-6400</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-5200</v>
       </c>
       <c r="K35" s="3">
         <v>-5900</v>
       </c>
       <c r="L35" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="M35" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="N35" s="3">
         <v>-2800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-2500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-3200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-1700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-2300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-200</v>
-      </c>
-      <c r="W35" s="3">
-        <v>-200</v>
-      </c>
-      <c r="X35" s="3">
-        <v>-100</v>
       </c>
       <c r="Y35" s="3">
         <v>-200</v>
       </c>
       <c r="Z35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-200</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +3059,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,74 +3090,76 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F41" s="3">
         <v>6400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>15700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>16800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>28400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>32000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>36000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>42700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>45700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>47500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>49200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>5600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>8100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>8800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>9800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>11100</v>
       </c>
-      <c r="S41" s="3">
-        <v>0</v>
-      </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
+        <v>0</v>
+      </c>
+      <c r="V41" s="3">
         <v>100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>300</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2996,8 +3169,14 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3073,8 +3252,14 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3111,27 +3296,27 @@
       <c r="N43" s="3">
         <v>0</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
+      <c r="O43" s="3">
+        <v>0</v>
       </c>
       <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3">
         <v>400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>200</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
-      </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
         <v>700</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3141,17 +3326,23 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z43" s="3">
-        <v>0</v>
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3227,74 +3418,80 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F45" s="3">
         <v>3900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>7100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>8800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>7600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>600</v>
-      </c>
-      <c r="K45" s="3">
-        <v>300</v>
-      </c>
-      <c r="L45" s="3">
-        <v>200</v>
       </c>
       <c r="M45" s="3">
         <v>300</v>
       </c>
       <c r="N45" s="3">
+        <v>200</v>
+      </c>
+      <c r="O45" s="3">
+        <v>300</v>
+      </c>
+      <c r="P45" s="3">
         <v>400</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3">
         <v>100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>300</v>
       </c>
-      <c r="S45" s="3">
-        <v>0</v>
-      </c>
-      <c r="T45" s="3">
-        <v>0</v>
-      </c>
       <c r="U45" s="3">
         <v>0</v>
       </c>
       <c r="V45" s="3">
+        <v>0</v>
+      </c>
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+      <c r="X45" s="3">
         <v>100</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3304,74 +3501,80 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E46" s="3">
         <v>10200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
+        <v>10200</v>
+      </c>
+      <c r="G46" s="3">
         <v>22800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>25500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>36000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>32500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>36500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>43300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>46000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>47700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>49500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>6000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>8100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>9400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>10200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>11400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>400</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3381,8 +3584,14 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3458,8 +3667,14 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3535,8 +3750,14 @@
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3612,8 +3833,14 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3916,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,8 +3999,14 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3817,22 +4056,22 @@
         <v>0</v>
       </c>
       <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
         <v>400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>200</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
-      </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
+      <c r="X52" s="3">
+        <v>0</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
@@ -3843,8 +4082,14 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,73 +4165,79 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E54" s="3">
         <v>10200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
+        <v>10200</v>
+      </c>
+      <c r="G54" s="3">
         <v>22800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>25500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>36000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>32500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>36500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>43300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>46000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>47700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>49500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>6000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>8100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>9400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>10200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>11400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1100</v>
-      </c>
-      <c r="T54" s="3">
-        <v>400</v>
-      </c>
-      <c r="U54" s="3">
-        <v>300</v>
       </c>
       <c r="V54" s="3">
         <v>400</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
+      <c r="W54" s="3">
+        <v>300</v>
+      </c>
+      <c r="X54" s="3">
+        <v>400</v>
       </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
@@ -3997,8 +4248,14 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4283,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,73 +4314,75 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F57" s="3">
         <v>1900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>4200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>4000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>300</v>
-      </c>
-      <c r="P57" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>100</v>
       </c>
       <c r="R57" s="3">
         <v>100</v>
       </c>
       <c r="S57" s="3">
+        <v>100</v>
+      </c>
+      <c r="T57" s="3">
+        <v>100</v>
+      </c>
+      <c r="U57" s="3">
         <v>1200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>400</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
-      </c>
-      <c r="V57" s="3">
-        <v>0</v>
-      </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+      <c r="X57" s="3">
+        <v>0</v>
       </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
@@ -4132,8 +4393,14 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4209,37 +4476,43 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F59" s="3">
         <v>1600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>3700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>300</v>
-      </c>
-      <c r="K59" s="3">
-        <v>800</v>
-      </c>
-      <c r="L59" s="3">
-        <v>800</v>
       </c>
       <c r="M59" s="3">
         <v>800</v>
@@ -4248,19 +4521,19 @@
         <v>800</v>
       </c>
       <c r="O59" s="3">
+        <v>800</v>
+      </c>
+      <c r="P59" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q59" s="3">
         <v>200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>600</v>
-      </c>
-      <c r="R59" s="3">
-        <v>700</v>
-      </c>
-      <c r="S59" s="3">
-        <v>800</v>
       </c>
       <c r="T59" s="3">
         <v>700</v>
@@ -4269,14 +4542,14 @@
         <v>800</v>
       </c>
       <c r="V59" s="3">
+        <v>700</v>
+      </c>
+      <c r="W59" s="3">
+        <v>800</v>
+      </c>
+      <c r="X59" s="3">
         <v>600</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4286,74 +4559,80 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F60" s="3">
         <v>3600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>5400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>7700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>2000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>600</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4363,8 +4642,14 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4414,10 +4699,10 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="T61" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="U61" s="3">
         <v>500</v>
@@ -4426,10 +4711,10 @@
         <v>500</v>
       </c>
       <c r="W61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="X61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="Y61" s="3">
         <v>0</v>
@@ -4440,31 +4725,37 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+        <v>13700</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -4491,22 +4782,22 @@
         <v>0</v>
       </c>
       <c r="S62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U62" s="3">
         <v>100</v>
       </c>
       <c r="V62" s="3">
-        <v>0</v>
-      </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="W62" s="3">
+        <v>100</v>
+      </c>
+      <c r="X62" s="3">
+        <v>0</v>
       </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
@@ -4517,8 +4808,14 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4891,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4974,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,74 +5057,80 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>18000</v>
+      </c>
+      <c r="F66" s="3">
         <v>3600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>5400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>7700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>2600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1100</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4825,8 +5140,14 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5175,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5254,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5337,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5059,10 +5394,10 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
-        <v>7100</v>
+        <v>0</v>
       </c>
       <c r="T70" s="3">
-        <v>7100</v>
+        <v>0</v>
       </c>
       <c r="U70" s="3">
         <v>7100</v>
@@ -5071,10 +5406,10 @@
         <v>7100</v>
       </c>
       <c r="W70" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="X70" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="Y70" s="3">
         <v>0</v>
@@ -5085,8 +5420,14 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,74 +5503,80 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-111300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-110300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-88000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-73300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-63800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-54100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-51000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-43300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-34600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-28700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-22800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-20000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-17400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-14200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-12500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-11500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-9200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-8800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-8600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-8300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-8000</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5239,8 +5586,14 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5669,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5752,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,74 +5835,80 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="F76" s="3">
         <v>6700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>20700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>20100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>28300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>30000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>35200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>42000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>44500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>46500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>48600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>4400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>7500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>9100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>9500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>10700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>-8600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>-8400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>-8100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>-7800</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5547,8 +5918,14 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,167 +6001,185 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-22200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-14700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-9500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-9700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-3100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-6400</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-5200</v>
       </c>
       <c r="K81" s="3">
         <v>-5900</v>
       </c>
       <c r="L81" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="M81" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="N81" s="3">
         <v>-2800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-2500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-3200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-1700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-2300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-200</v>
-      </c>
-      <c r="W81" s="3">
-        <v>-200</v>
-      </c>
-      <c r="X81" s="3">
-        <v>-100</v>
       </c>
       <c r="Y81" s="3">
         <v>-200</v>
       </c>
       <c r="Z81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-200</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,8 +6207,10 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5889,8 +6286,14 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6369,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6452,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6535,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6618,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,85 +6701,97 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-9400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="G89" s="3">
         <v>-9600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-11600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-3600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-4000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-6700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-3000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-3100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-2500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-1300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-1000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-100</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3">
         <v>-200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-200</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,8 +6819,10 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6457,8 +6898,14 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6981,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,8 +7064,14 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6688,8 +7147,14 @@
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,8 +7182,10 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6794,8 +7261,14 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7344,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7427,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,23 +7510,29 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="E100" s="3">
+        <v>8800</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>8600</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
@@ -7058,14 +7549,14 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>46800</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
@@ -7073,37 +7564,43 @@
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>12100</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>-100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>500</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>200</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7179,81 +7676,93 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F102" s="3">
         <v>-9400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-11600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-3600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-4000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-6700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-3000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-1800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>43600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-2500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>11100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-100</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>-200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>100</v>
       </c>
-      <c r="AA102" s="3" t="s">
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ANVS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANVS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
   <si>
     <t>ANVS</t>
   </si>
@@ -656,129 +656,133 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -860,8 +864,11 @@
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -943,8 +950,11 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1026,8 +1036,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,68 +1070,69 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E12" s="3">
         <v>6500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>13800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>8300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>7800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>800</v>
       </c>
-      <c r="V12" s="3">
-        <v>0</v>
-      </c>
       <c r="W12" s="3">
         <v>0</v>
       </c>
@@ -1126,22 +1140,25 @@
         <v>0</v>
       </c>
       <c r="Y12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="3">
         <v>200</v>
       </c>
-      <c r="Z12" s="3">
-        <v>0</v>
-      </c>
       <c r="AA12" s="3">
         <v>0</v>
       </c>
       <c r="AB12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="3">
         <v>100</v>
       </c>
-      <c r="AC12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,8 +1240,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1243,8 +1263,8 @@
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1268,23 +1288,23 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-600</v>
-      </c>
-      <c r="S14" s="3">
-        <v>-200</v>
       </c>
       <c r="T14" s="3">
         <v>-200</v>
       </c>
       <c r="U14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V14" s="3">
         <v>-700</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1297,8 +1317,8 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1306,8 +1326,11 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1389,8 +1412,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,8 +1443,9 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1426,82 +1453,85 @@
         <v>7800</v>
       </c>
       <c r="E17" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F17" s="3">
         <v>10400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>10000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>300</v>
-      </c>
-      <c r="X17" s="3">
-        <v>200</v>
       </c>
       <c r="Y17" s="3">
         <v>200</v>
       </c>
       <c r="Z17" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA17" s="3">
         <v>100</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>200</v>
       </c>
       <c r="AB17" s="3">
         <v>200</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1509,82 +1539,85 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-10400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-14900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-9800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-10000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-6500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-300</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-200</v>
       </c>
       <c r="Y18" s="3">
         <v>-200</v>
       </c>
       <c r="Z18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-100</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-200</v>
       </c>
       <c r="AB18" s="3">
         <v>-200</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,8 +1647,9 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1623,25 +1657,25 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F20" s="3">
         <v>-11800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>200</v>
       </c>
       <c r="H20" s="3">
         <v>200</v>
       </c>
       <c r="I20" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J20" s="3">
         <v>100</v>
       </c>
       <c r="K20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1671,11 +1705,11 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -1694,23 +1728,26 @@
       <c r="AB20" s="3">
         <v>0</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="3">
         <v>-22200</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1780,8 +1817,11 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1863,91 +1903,97 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-22200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-14700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-9500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-6400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-200</v>
-      </c>
-      <c r="V23" s="3">
-        <v>-300</v>
       </c>
       <c r="W23" s="3">
         <v>-300</v>
       </c>
       <c r="X23" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="Y23" s="3">
         <v>-200</v>
       </c>
       <c r="Z23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-100</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>-200</v>
       </c>
       <c r="AB23" s="3">
         <v>-200</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2029,8 +2075,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2161,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-22200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-14700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-200</v>
-      </c>
-      <c r="V26" s="3">
-        <v>-300</v>
       </c>
       <c r="W26" s="3">
         <v>-300</v>
       </c>
       <c r="X26" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="Y26" s="3">
         <v>-200</v>
       </c>
       <c r="Z26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-100</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>-200</v>
       </c>
       <c r="AB26" s="3">
         <v>-200</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-22200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-14700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-200</v>
-      </c>
-      <c r="V27" s="3">
-        <v>-300</v>
       </c>
       <c r="W27" s="3">
         <v>-300</v>
       </c>
       <c r="X27" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="Y27" s="3">
         <v>-200</v>
       </c>
       <c r="Z27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-100</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>-200</v>
       </c>
       <c r="AB27" s="3">
         <v>-200</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,8 +2677,11 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2619,25 +2689,25 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="F32" s="3">
         <v>11800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-200</v>
       </c>
       <c r="H32" s="3">
         <v>-200</v>
       </c>
       <c r="I32" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="J32" s="3">
         <v>-100</v>
       </c>
       <c r="K32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -2667,11 +2737,11 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -2690,94 +2760,100 @@
       <c r="AB32" s="3">
         <v>0</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-22200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-14700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-200</v>
-      </c>
-      <c r="V33" s="3">
-        <v>-300</v>
       </c>
       <c r="W33" s="3">
         <v>-300</v>
       </c>
       <c r="X33" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="Y33" s="3">
         <v>-200</v>
       </c>
       <c r="Z33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-100</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>-200</v>
       </c>
       <c r="AB33" s="3">
         <v>-200</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2935,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-22200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-14700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-200</v>
-      </c>
-      <c r="V35" s="3">
-        <v>-300</v>
       </c>
       <c r="W35" s="3">
         <v>-300</v>
       </c>
       <c r="X35" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="Y35" s="3">
         <v>-200</v>
       </c>
       <c r="Z35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-100</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>-200</v>
       </c>
       <c r="AB35" s="3">
         <v>-200</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,77 +3178,78 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>15700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>28400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>32000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>36000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>42700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>45700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>47500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>49200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>11100</v>
       </c>
-      <c r="U41" s="3">
-        <v>0</v>
-      </c>
       <c r="V41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W41" s="3">
         <v>100</v>
       </c>
       <c r="X41" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y41" s="3">
         <v>300</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3175,8 +3262,11 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3258,8 +3348,11 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3302,24 +3395,24 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R43" s="3">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3">
         <v>400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>200</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
-      </c>
       <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3">
         <v>700</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3332,8 +3425,8 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA43" s="3">
-        <v>0</v>
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB43" s="3">
         <v>0</v>
@@ -3341,8 +3434,11 @@
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3424,65 +3520,68 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E45" s="3">
         <v>4700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>500</v>
-      </c>
-      <c r="K45" s="3">
-        <v>600</v>
       </c>
       <c r="L45" s="3">
         <v>600</v>
       </c>
       <c r="M45" s="3">
+        <v>600</v>
+      </c>
+      <c r="N45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>400</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3">
         <v>100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>300</v>
       </c>
-      <c r="U45" s="3">
-        <v>0</v>
-      </c>
       <c r="V45" s="3">
         <v>0</v>
       </c>
@@ -3490,11 +3589,11 @@
         <v>0</v>
       </c>
       <c r="X45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
         <v>100</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3507,77 +3606,80 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E46" s="3">
         <v>7800</v>
-      </c>
-      <c r="E46" s="3">
-        <v>10200</v>
       </c>
       <c r="F46" s="3">
         <v>10200</v>
       </c>
       <c r="G46" s="3">
+        <v>10200</v>
+      </c>
+      <c r="H46" s="3">
         <v>22800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>25500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>36000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>32500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>36500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>43300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>46000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>47700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>49500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>10200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>11400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>700</v>
-      </c>
-      <c r="V46" s="3">
-        <v>100</v>
       </c>
       <c r="W46" s="3">
         <v>100</v>
       </c>
       <c r="X46" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y46" s="3">
         <v>400</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3590,8 +3692,11 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3673,8 +3778,11 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3756,8 +3864,11 @@
       <c r="AC48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3839,8 +3950,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,8 +4122,11 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4062,19 +4182,19 @@
         <v>0</v>
       </c>
       <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
         <v>400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>200</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
+      <c r="Y52" s="3">
+        <v>0</v>
       </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
@@ -4088,8 +4208,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,77 +4294,80 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E54" s="3">
         <v>7800</v>
-      </c>
-      <c r="E54" s="3">
-        <v>10200</v>
       </c>
       <c r="F54" s="3">
         <v>10200</v>
       </c>
       <c r="G54" s="3">
+        <v>10200</v>
+      </c>
+      <c r="H54" s="3">
         <v>22800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>25500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>36000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>32500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>36500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>43300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>46000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>47700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>49500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>9400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>10200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>11400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>400</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4254,8 +4380,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,55 +4446,56 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E57" s="3">
         <v>4100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1800</v>
-      </c>
-      <c r="K57" s="3">
-        <v>900</v>
       </c>
       <c r="L57" s="3">
         <v>900</v>
       </c>
       <c r="M57" s="3">
+        <v>900</v>
+      </c>
+      <c r="N57" s="3">
         <v>700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>300</v>
-      </c>
-      <c r="R57" s="3">
-        <v>100</v>
       </c>
       <c r="S57" s="3">
         <v>100</v>
@@ -4373,19 +4504,19 @@
         <v>100</v>
       </c>
       <c r="U57" s="3">
+        <v>100</v>
+      </c>
+      <c r="V57" s="3">
         <v>1200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>400</v>
       </c>
-      <c r="W57" s="3">
-        <v>0</v>
-      </c>
       <c r="X57" s="3">
         <v>0</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
+      <c r="Y57" s="3">
+        <v>0</v>
       </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
@@ -4399,8 +4530,11 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4482,40 +4616,43 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>700</v>
+      </c>
+      <c r="E59" s="3">
         <v>800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>300</v>
-      </c>
-      <c r="M59" s="3">
-        <v>800</v>
       </c>
       <c r="N59" s="3">
         <v>800</v>
@@ -4527,32 +4664,32 @@
         <v>800</v>
       </c>
       <c r="Q59" s="3">
+        <v>800</v>
+      </c>
+      <c r="R59" s="3">
         <v>200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>600</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4565,77 +4702,80 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E60" s="3">
         <v>4900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2500</v>
-      </c>
-      <c r="K60" s="3">
-        <v>1300</v>
       </c>
       <c r="L60" s="3">
         <v>1300</v>
       </c>
       <c r="M60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N60" s="3">
         <v>1500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>300</v>
-      </c>
-      <c r="S60" s="3">
-        <v>700</v>
       </c>
       <c r="T60" s="3">
         <v>700</v>
       </c>
       <c r="U60" s="3">
+        <v>700</v>
+      </c>
+      <c r="V60" s="3">
         <v>2000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>600</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4648,8 +4788,11 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4705,7 +4848,7 @@
         <v>0</v>
       </c>
       <c r="U61" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="V61" s="3">
         <v>500</v>
@@ -4717,7 +4860,7 @@
         <v>500</v>
       </c>
       <c r="Y61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="Z61" s="3">
         <v>0</v>
@@ -4731,20 +4874,23 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E62" s="3">
         <v>6300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13700</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4757,8 +4903,8 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -4788,7 +4934,7 @@
         <v>0</v>
       </c>
       <c r="U62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V62" s="3">
         <v>100</v>
@@ -4797,10 +4943,10 @@
         <v>100</v>
       </c>
       <c r="X62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>0</v>
       </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
@@ -4814,8 +4960,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,77 +5218,80 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E66" s="3">
         <v>11200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>18000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2500</v>
-      </c>
-      <c r="K66" s="3">
-        <v>1300</v>
       </c>
       <c r="L66" s="3">
         <v>1300</v>
       </c>
       <c r="M66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N66" s="3">
         <v>1500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>300</v>
-      </c>
-      <c r="S66" s="3">
-        <v>700</v>
       </c>
       <c r="T66" s="3">
         <v>700</v>
       </c>
       <c r="U66" s="3">
+        <v>700</v>
+      </c>
+      <c r="V66" s="3">
         <v>2600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1100</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5146,8 +5304,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5400,7 +5568,7 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
-        <v>7100</v>
+        <v>0</v>
       </c>
       <c r="V70" s="3">
         <v>7100</v>
@@ -5412,7 +5580,7 @@
         <v>7100</v>
       </c>
       <c r="Y70" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="Z70" s="3">
         <v>0</v>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,77 +5680,80 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-116300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-111300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-110300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-88000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-73300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-63800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-54100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-51000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-43300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-34600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-28700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-22800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-20000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-17400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-14200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-12500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-11500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-9200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-8800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-8600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-8300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5592,8 +5766,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,77 +6024,80 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-3400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-7800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>28300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>30000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>35200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>42000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>44500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>46500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>48600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>10700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-8600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-8400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-8100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-7800</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5924,8 +6110,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6196,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-22200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-14700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-200</v>
-      </c>
-      <c r="V81" s="3">
-        <v>-300</v>
       </c>
       <c r="W81" s="3">
         <v>-300</v>
       </c>
       <c r="X81" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="Y81" s="3">
         <v>-200</v>
       </c>
       <c r="Z81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-100</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>-200</v>
       </c>
       <c r="AB81" s="3">
         <v>-200</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,8 +6407,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6292,8 +6491,11 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,91 +6921,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7000</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-9400</v>
       </c>
       <c r="F89" s="3">
         <v>-9400</v>
       </c>
       <c r="G89" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="H89" s="3">
         <v>-9600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-11600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-100</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
       <c r="W89" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="X89" s="3">
         <v>-200</v>
       </c>
       <c r="Y89" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="Z89" s="3">
         <v>-100</v>
       </c>
       <c r="AA89" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="AB89" s="3">
         <v>-200</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,8 +7041,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6904,8 +7125,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,8 +7297,11 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7153,8 +7383,11 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7417,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,26 +7759,29 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E100" s="3">
         <v>4400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>8800</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>8600</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
@@ -7555,11 +7801,11 @@
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>46800</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
@@ -7570,23 +7816,23 @@
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>12100</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>-100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>500</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
@@ -7594,13 +7840,16 @@
         <v>0</v>
       </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>200</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7682,87 +7931,93 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-9400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-11600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-6700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3000</v>
-      </c>
-      <c r="M102" s="3">
-        <v>-1800</v>
       </c>
       <c r="N102" s="3">
         <v>-1800</v>
       </c>
       <c r="O102" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="P102" s="3">
         <v>43600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>11100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-100</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>-200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>300</v>
-      </c>
-      <c r="Y102" s="3">
-        <v>-100</v>
       </c>
       <c r="Z102" s="3">
         <v>-100</v>
       </c>
       <c r="AA102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>100</v>
       </c>
-      <c r="AC102" s="3" t="s">
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ANVS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANVS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="92">
   <si>
     <t>ANVS</t>
   </si>
@@ -656,156 +656,160 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -867,8 +871,11 @@
       <c r="AD8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -953,8 +960,11 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1039,8 +1049,11 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1071,71 +1084,72 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E12" s="3">
         <v>5800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>8900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>13800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>8300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>7800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>800</v>
       </c>
-      <c r="W12" s="3">
-        <v>0</v>
-      </c>
       <c r="X12" s="3">
         <v>0</v>
       </c>
@@ -1143,22 +1157,25 @@
         <v>0</v>
       </c>
       <c r="Z12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="3">
         <v>200</v>
       </c>
-      <c r="AA12" s="3">
-        <v>0</v>
-      </c>
       <c r="AB12" s="3">
         <v>0</v>
       </c>
       <c r="AC12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="3">
         <v>100</v>
       </c>
-      <c r="AD12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1243,8 +1260,11 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1266,8 +1286,8 @@
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1291,23 +1311,23 @@
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-600</v>
-      </c>
-      <c r="T14" s="3">
-        <v>-200</v>
       </c>
       <c r="U14" s="3">
         <v>-200</v>
       </c>
       <c r="V14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W14" s="3">
         <v>-700</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1320,8 +1340,8 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1329,8 +1349,11 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1415,8 +1438,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,180 +1470,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7800</v>
+        <v>4400</v>
       </c>
       <c r="E17" s="3">
         <v>7800</v>
       </c>
       <c r="F17" s="3">
+        <v>7800</v>
+      </c>
+      <c r="G17" s="3">
         <v>10400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>10000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>300</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>200</v>
       </c>
       <c r="Z17" s="3">
         <v>200</v>
       </c>
       <c r="AA17" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB17" s="3">
         <v>100</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>200</v>
       </c>
       <c r="AC17" s="3">
         <v>200</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-4400</v>
       </c>
       <c r="E18" s="3">
         <v>-7800</v>
       </c>
       <c r="F18" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="G18" s="3">
         <v>-10400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-14900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-9800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-10000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-300</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-200</v>
       </c>
       <c r="Z18" s="3">
         <v>-200</v>
       </c>
       <c r="AA18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-100</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>-200</v>
       </c>
       <c r="AC18" s="3">
         <v>-200</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1648,37 +1681,38 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>8400</v>
       </c>
       <c r="E20" s="3">
-        <v>6700</v>
+        <v>-2700</v>
       </c>
       <c r="F20" s="3">
-        <v>-11800</v>
+        <v>-6700</v>
       </c>
       <c r="G20" s="3">
-        <v>100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>200</v>
-      </c>
-      <c r="I20" s="3">
-        <v>200</v>
-      </c>
-      <c r="J20" s="3">
-        <v>100</v>
+        <v>11800</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
       </c>
       <c r="L20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1708,11 +1742,11 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
@@ -1731,34 +1765,37 @@
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-5000</v>
       </c>
       <c r="F21" s="3">
-        <v>-22200</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>-1100</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-10000</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1820,31 +1857,34 @@
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1906,117 +1946,123 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-22200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-14700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-6400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-200</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-300</v>
       </c>
       <c r="X23" s="3">
         <v>-300</v>
       </c>
       <c r="Y23" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="Z23" s="3">
         <v>-200</v>
       </c>
       <c r="AA23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AB23" s="3">
         <v>-100</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>-200</v>
       </c>
       <c r="AC23" s="3">
         <v>-200</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -2078,8 +2124,11 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2213,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-22200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-14700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-6400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-200</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-300</v>
       </c>
       <c r="X26" s="3">
         <v>-300</v>
       </c>
       <c r="Y26" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="Z26" s="3">
         <v>-200</v>
       </c>
       <c r="AA26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AB26" s="3">
         <v>-100</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>-200</v>
       </c>
       <c r="AC26" s="3">
         <v>-200</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-22200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-14700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-200</v>
-      </c>
-      <c r="W27" s="3">
-        <v>-300</v>
       </c>
       <c r="X27" s="3">
         <v>-300</v>
       </c>
       <c r="Y27" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="Z27" s="3">
         <v>-200</v>
       </c>
       <c r="AA27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AB27" s="3">
         <v>-100</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>-200</v>
       </c>
       <c r="AC27" s="3">
         <v>-200</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2480,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2508,8 +2569,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2658,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,37 +2747,40 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-8400</v>
       </c>
       <c r="E32" s="3">
-        <v>-6700</v>
+        <v>2700</v>
       </c>
       <c r="F32" s="3">
-        <v>11800</v>
+        <v>6700</v>
       </c>
       <c r="G32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-100</v>
+        <v>-11800</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
       </c>
       <c r="L32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -2740,11 +2810,11 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
@@ -2763,97 +2833,103 @@
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-22200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-14700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-200</v>
-      </c>
-      <c r="W33" s="3">
-        <v>-300</v>
       </c>
       <c r="X33" s="3">
         <v>-300</v>
       </c>
       <c r="Y33" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="Z33" s="3">
         <v>-200</v>
       </c>
       <c r="AA33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AB33" s="3">
         <v>-100</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>-200</v>
       </c>
       <c r="AC33" s="3">
         <v>-200</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3014,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-22200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-14700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-200</v>
-      </c>
-      <c r="W35" s="3">
-        <v>-300</v>
       </c>
       <c r="X35" s="3">
         <v>-300</v>
       </c>
       <c r="Y35" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="Z35" s="3">
         <v>-200</v>
       </c>
       <c r="AA35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AB35" s="3">
         <v>-100</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>-200</v>
       </c>
       <c r="AC35" s="3">
         <v>-200</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3232,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,80 +3265,81 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E41" s="3">
         <v>4000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>28400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>32000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>36000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>42700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>45700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>47500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>49200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>11100</v>
       </c>
-      <c r="V41" s="3">
-        <v>0</v>
-      </c>
       <c r="W41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X41" s="3">
         <v>100</v>
       </c>
       <c r="Y41" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z41" s="3">
         <v>300</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3265,8 +3352,11 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3351,31 +3441,34 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3398,24 +3491,24 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S43" s="3">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T43" s="3">
         <v>400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>200</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
-      </c>
       <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3">
         <v>700</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3428,8 +3521,8 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB43" s="3">
-        <v>0</v>
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC43" s="3">
         <v>0</v>
@@ -3437,31 +3530,34 @@
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3523,68 +3619,71 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="E45" s="3">
-        <v>4700</v>
+        <v>700</v>
       </c>
       <c r="F45" s="3">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="G45" s="3">
-        <v>3900</v>
+        <v>4400</v>
       </c>
       <c r="H45" s="3">
-        <v>7100</v>
+        <v>3700</v>
       </c>
       <c r="I45" s="3">
-        <v>8800</v>
+        <v>6900</v>
       </c>
       <c r="J45" s="3">
+        <v>8600</v>
+      </c>
+      <c r="K45" s="3">
         <v>7600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>500</v>
-      </c>
-      <c r="L45" s="3">
-        <v>600</v>
       </c>
       <c r="M45" s="3">
         <v>600</v>
       </c>
       <c r="N45" s="3">
+        <v>600</v>
+      </c>
+      <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>400</v>
       </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
       <c r="S45" s="3">
+        <v>0</v>
+      </c>
+      <c r="T45" s="3">
         <v>100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>300</v>
       </c>
-      <c r="V45" s="3">
-        <v>0</v>
-      </c>
       <c r="W45" s="3">
         <v>0</v>
       </c>
@@ -3592,11 +3691,11 @@
         <v>0</v>
       </c>
       <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="3">
         <v>100</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3609,80 +3708,83 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E46" s="3">
         <v>5000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7800</v>
-      </c>
-      <c r="F46" s="3">
-        <v>10200</v>
       </c>
       <c r="G46" s="3">
         <v>10200</v>
       </c>
       <c r="H46" s="3">
+        <v>10200</v>
+      </c>
+      <c r="I46" s="3">
         <v>22800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>25500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>36000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>32500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>36500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>43300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>46000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>47700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>49500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>10200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>11400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>700</v>
-      </c>
-      <c r="W46" s="3">
-        <v>100</v>
       </c>
       <c r="X46" s="3">
         <v>100</v>
       </c>
       <c r="Y46" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z46" s="3">
         <v>400</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3695,31 +3797,34 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3781,31 +3886,34 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>0</v>
-      </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -3867,8 +3975,11 @@
       <c r="AD48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3953,8 +4064,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4153,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,31 +4242,34 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -4185,19 +4305,19 @@
         <v>0</v>
       </c>
       <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3">
         <v>400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>200</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
+      <c r="Z52" s="3">
+        <v>0</v>
       </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
@@ -4211,8 +4331,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,80 +4420,83 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E54" s="3">
         <v>5000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7800</v>
-      </c>
-      <c r="F54" s="3">
-        <v>10200</v>
       </c>
       <c r="G54" s="3">
         <v>10200</v>
       </c>
       <c r="H54" s="3">
+        <v>10200</v>
+      </c>
+      <c r="I54" s="3">
         <v>22800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>25500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>36000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>32500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>36500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>43300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>46000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>47700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>49500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>9400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>11400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>400</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4383,8 +4509,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4544,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,58 +4577,59 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E57" s="3">
         <v>3400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1800</v>
-      </c>
-      <c r="L57" s="3">
-        <v>900</v>
       </c>
       <c r="M57" s="3">
         <v>900</v>
       </c>
       <c r="N57" s="3">
+        <v>900</v>
+      </c>
+      <c r="O57" s="3">
         <v>700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>300</v>
-      </c>
-      <c r="S57" s="3">
-        <v>100</v>
       </c>
       <c r="T57" s="3">
         <v>100</v>
@@ -4507,19 +4638,19 @@
         <v>100</v>
       </c>
       <c r="V57" s="3">
+        <v>100</v>
+      </c>
+      <c r="W57" s="3">
         <v>1200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>400</v>
       </c>
-      <c r="X57" s="3">
-        <v>0</v>
-      </c>
       <c r="Y57" s="3">
         <v>0</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
+      <c r="Z57" s="3">
+        <v>0</v>
       </c>
       <c r="AA57" s="3" t="s">
         <v>3</v>
@@ -4533,8 +4664,11 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4619,43 +4753,46 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
+        <v>3700</v>
+      </c>
+      <c r="L59" s="3">
         <v>700</v>
       </c>
-      <c r="E59" s="3">
-        <v>800</v>
-      </c>
-      <c r="F59" s="3">
-        <v>3000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H59" s="3">
-        <v>900</v>
-      </c>
-      <c r="I59" s="3">
-        <v>1300</v>
-      </c>
-      <c r="J59" s="3">
-        <v>3700</v>
-      </c>
-      <c r="K59" s="3">
-        <v>700</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>300</v>
-      </c>
-      <c r="N59" s="3">
-        <v>800</v>
       </c>
       <c r="O59" s="3">
         <v>800</v>
@@ -4667,32 +4804,32 @@
         <v>800</v>
       </c>
       <c r="R59" s="3">
+        <v>800</v>
+      </c>
+      <c r="S59" s="3">
         <v>200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>600</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4705,80 +4842,83 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E60" s="3">
         <v>4100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2500</v>
-      </c>
-      <c r="L60" s="3">
-        <v>1300</v>
       </c>
       <c r="M60" s="3">
         <v>1300</v>
       </c>
       <c r="N60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="O60" s="3">
         <v>1500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>300</v>
-      </c>
-      <c r="T60" s="3">
-        <v>700</v>
       </c>
       <c r="U60" s="3">
         <v>700</v>
       </c>
       <c r="V60" s="3">
+        <v>700</v>
+      </c>
+      <c r="W60" s="3">
         <v>2000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>600</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4791,8 +4931,11 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4851,7 +4994,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="W61" s="3">
         <v>500</v>
@@ -4863,7 +5006,7 @@
         <v>500</v>
       </c>
       <c r="Z61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AA61" s="3">
         <v>0</v>
@@ -4877,23 +5020,26 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E62" s="3">
         <v>2700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13700</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4906,8 +5052,8 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -4937,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W62" s="3">
         <v>100</v>
@@ -4946,10 +5092,10 @@
         <v>100</v>
       </c>
       <c r="Y62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>0</v>
       </c>
       <c r="AA62" s="3" t="s">
         <v>3</v>
@@ -4963,8 +5109,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5198,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5287,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,80 +5376,83 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E66" s="3">
         <v>6800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>18000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2500</v>
-      </c>
-      <c r="L66" s="3">
-        <v>1300</v>
       </c>
       <c r="M66" s="3">
         <v>1300</v>
       </c>
       <c r="N66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="O66" s="3">
         <v>1500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>300</v>
-      </c>
-      <c r="T66" s="3">
-        <v>700</v>
       </c>
       <c r="U66" s="3">
         <v>700</v>
       </c>
       <c r="V66" s="3">
+        <v>700</v>
+      </c>
+      <c r="W66" s="3">
         <v>2600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1100</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5307,8 +5465,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5500,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5587,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5676,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5571,7 +5739,7 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
-        <v>7100</v>
+        <v>0</v>
       </c>
       <c r="W70" s="3">
         <v>7100</v>
@@ -5583,7 +5751,7 @@
         <v>7100</v>
       </c>
       <c r="Z70" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="AA70" s="3">
         <v>0</v>
@@ -5597,8 +5765,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,80 +5854,83 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-129000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-116300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-111300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-110300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-88000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-73300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-63800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-54100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-51000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-43300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-34600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-28700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-22800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-17400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-14200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-12500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-11500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-9200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-8800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-8600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5769,8 +5943,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6032,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6121,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,80 +6210,83 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-3400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-7800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>20100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>28300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>30000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>35200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>42000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>44500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>46500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>48600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-8600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-8400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-8100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-7800</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6113,8 +6299,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6388,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-22200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-14700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-200</v>
-      </c>
-      <c r="W81" s="3">
-        <v>-300</v>
       </c>
       <c r="X81" s="3">
         <v>-300</v>
       </c>
       <c r="Y81" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="Z81" s="3">
         <v>-200</v>
       </c>
       <c r="AA81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AB81" s="3">
         <v>-100</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>-200</v>
       </c>
       <c r="AC81" s="3">
         <v>-200</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,31 +6606,32 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -6494,8 +6693,11 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6782,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6871,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6960,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7049,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,94 +7138,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7000</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-9400</v>
       </c>
       <c r="G89" s="3">
         <v>-9400</v>
       </c>
       <c r="H89" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="I89" s="3">
         <v>-9600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-11600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-100</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
       <c r="X89" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="Y89" s="3">
         <v>-200</v>
       </c>
       <c r="Z89" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AA89" s="3">
         <v>-100</v>
       </c>
       <c r="AB89" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="AC89" s="3">
         <v>-200</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,31 +7262,32 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -7128,8 +7349,11 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7438,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,31 +7527,34 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -7386,8 +7616,11 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,31 +7651,32 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7504,8 +7738,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7827,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7916,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,29 +8005,32 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E100" s="3">
         <v>4200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>8800</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>8600</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
@@ -7804,11 +8050,11 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>46800</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
@@ -7819,23 +8065,23 @@
         <v>0</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>12100</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>500</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
@@ -7843,36 +8089,39 @@
         <v>0</v>
       </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>200</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7934,90 +8183,96 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E102" s="3">
         <v>900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-9400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-11600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3000</v>
-      </c>
-      <c r="N102" s="3">
-        <v>-1800</v>
       </c>
       <c r="O102" s="3">
         <v>-1800</v>
       </c>
       <c r="P102" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="Q102" s="3">
         <v>43600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>11100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-100</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>300</v>
-      </c>
-      <c r="Z102" s="3">
-        <v>-100</v>
       </c>
       <c r="AA102" s="3">
         <v>-100</v>
       </c>
       <c r="AB102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>100</v>
       </c>
-      <c r="AD102" s="3" t="s">
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ANVS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANVS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="92">
   <si>
     <t>ANVS</t>
   </si>
@@ -656,137 +656,144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -811,11 +818,11 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -874,8 +881,14 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -963,8 +976,14 @@
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1052,8 +1071,14 @@
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1085,97 +1110,105 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F12" s="3">
         <v>2700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>5800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>6500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>8900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>13800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>8300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>7800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>1600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>4100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>4000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>2100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>2900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>1400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>1800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>2400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>1400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>800</v>
       </c>
-      <c r="X12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>0</v>
-      </c>
       <c r="Z12" s="3">
         <v>0</v>
       </c>
       <c r="AA12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="3">
         <v>200</v>
       </c>
-      <c r="AB12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>0</v>
-      </c>
       <c r="AD12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="3">
         <v>100</v>
       </c>
-      <c r="AE12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1263,8 +1296,14 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1289,11 +1328,11 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1314,26 +1353,26 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="T14" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="U14" s="3">
         <v>-200</v>
       </c>
       <c r="V14" s="3">
+        <v>-600</v>
+      </c>
+      <c r="W14" s="3">
         <v>-200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-700</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1343,17 +1382,23 @@
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1441,8 +1486,14 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1471,186 +1522,200 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F17" s="3">
         <v>4400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>7800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>7800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>10400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>14900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>9800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>10000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>6500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>6000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>5300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>5900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>3200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>2300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>100</v>
-      </c>
-      <c r="X17" s="3">
-        <v>200</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>300</v>
       </c>
       <c r="Z17" s="3">
         <v>200</v>
       </c>
       <c r="AA17" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB17" s="3">
         <v>200</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>100</v>
       </c>
       <c r="AC17" s="3">
         <v>200</v>
       </c>
       <c r="AD17" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE17" s="3">
         <v>200</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-4400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-7800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-7800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-10400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-14900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-9800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-10000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-3200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-6500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-6000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-5300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-5900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-2500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-3200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-1700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-1000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-2300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-100</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-300</v>
       </c>
       <c r="Z18" s="3">
         <v>-200</v>
       </c>
       <c r="AA18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-200</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>-100</v>
       </c>
       <c r="AC18" s="3">
         <v>-200</v>
       </c>
       <c r="AD18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-200</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1682,44 +1747,46 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F20" s="3">
         <v>8400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-2700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-6700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>11800</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1745,14 +1812,14 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
@@ -1768,41 +1835,47 @@
       <c r="AD20" s="3">
         <v>0</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-12800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-5000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-22300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-14900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-9800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-10000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1860,8 +1933,14 @@
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1886,11 +1965,11 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1949,97 +2028,109 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-12600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-5000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-22200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-14700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-9500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-9700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-3100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-6400</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-5200</v>
       </c>
       <c r="O23" s="3">
         <v>-5900</v>
       </c>
       <c r="P23" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="R23" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-2500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-3200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-1700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-1000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-2300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>-100</v>
       </c>
       <c r="AC23" s="3">
         <v>-200</v>
       </c>
       <c r="AD23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE23" s="3">
         <v>-200</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2064,11 +2155,11 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -2127,8 +2218,14 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2216,186 +2313,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-12600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-5000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-22200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-14700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-9500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-9700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-3100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-6400</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-5200</v>
       </c>
       <c r="O26" s="3">
         <v>-5900</v>
       </c>
       <c r="P26" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="R26" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-2500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-3200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-1700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-1000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-2300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>-100</v>
       </c>
       <c r="AC26" s="3">
         <v>-200</v>
       </c>
       <c r="AD26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE26" s="3">
         <v>-200</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-12600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-5000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-22200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-14700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-9500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-9700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-3100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-6400</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-5200</v>
       </c>
       <c r="O27" s="3">
         <v>-5900</v>
       </c>
       <c r="P27" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="R27" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-2500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-3200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-1700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-1000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-2300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>-100</v>
       </c>
       <c r="AC27" s="3">
         <v>-200</v>
       </c>
       <c r="AD27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE27" s="3">
         <v>-200</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2483,8 +2598,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2572,8 +2693,14 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2661,8 +2788,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2750,44 +2883,50 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>700</v>
+      </c>
+      <c r="F32" s="3">
         <v>-8400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>2700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>6700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-11800</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -2813,14 +2952,14 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
@@ -2836,100 +2975,112 @@
       <c r="AD32" s="3">
         <v>0</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-12600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-5000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-22200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-14700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-9500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-9700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-3100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-6400</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-5200</v>
       </c>
       <c r="O33" s="3">
         <v>-5900</v>
       </c>
       <c r="P33" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="R33" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-2500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-3200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-1700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-1000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-2300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>-100</v>
       </c>
       <c r="AC33" s="3">
         <v>-200</v>
       </c>
       <c r="AD33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE33" s="3">
         <v>-200</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3017,191 +3168,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-12600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-5000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-22200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-14700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-9500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-9700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-3100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-6400</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-5200</v>
       </c>
       <c r="O35" s="3">
         <v>-5900</v>
       </c>
       <c r="P35" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="R35" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-2500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-3200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-1700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-1000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-2300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>-100</v>
       </c>
       <c r="AC35" s="3">
         <v>-200</v>
       </c>
       <c r="AD35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE35" s="3">
         <v>-200</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3233,8 +3402,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3266,86 +3437,88 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>10600</v>
+      </c>
+      <c r="F41" s="3">
         <v>12600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>4000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>3100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>5800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>6400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>15700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>16800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>28400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>32000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>36000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>42700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>45700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>47500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>49200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>5600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>8100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>8800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>9800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>11100</v>
       </c>
-      <c r="W41" s="3">
-        <v>0</v>
-      </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="3">
         <v>100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>300</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3355,8 +3528,14 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3444,8 +3623,14 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3470,11 +3655,11 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -3494,27 +3679,27 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
+      <c r="S43" s="3">
+        <v>0</v>
       </c>
       <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V43" s="3">
         <v>400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>200</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
-      </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
         <v>700</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3524,17 +3709,23 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD43" s="3">
-        <v>0</v>
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3559,11 +3750,11 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3622,86 +3813,92 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F45" s="3">
         <v>1500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>4400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>4400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>3700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>6900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>8600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>7600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>600</v>
-      </c>
-      <c r="O45" s="3">
-        <v>300</v>
-      </c>
-      <c r="P45" s="3">
-        <v>200</v>
       </c>
       <c r="Q45" s="3">
         <v>300</v>
       </c>
       <c r="R45" s="3">
+        <v>200</v>
+      </c>
+      <c r="S45" s="3">
+        <v>300</v>
+      </c>
+      <c r="T45" s="3">
         <v>400</v>
       </c>
-      <c r="S45" s="3">
-        <v>0</v>
-      </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+      <c r="V45" s="3">
         <v>100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>300</v>
       </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
-      <c r="X45" s="3">
-        <v>0</v>
-      </c>
       <c r="Y45" s="3">
         <v>0</v>
       </c>
       <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="3">
         <v>100</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3711,86 +3908,92 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>13900</v>
+      </c>
+      <c r="F46" s="3">
         <v>14400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>5000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>7800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>10200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>10200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>22800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>25500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>36000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>32500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>36500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>43300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>46000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>47700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>49500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>6000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>8100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>9400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>10200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>11400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>400</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3800,8 +4003,14 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3826,11 +4035,11 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3889,8 +4098,14 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3915,11 +4130,11 @@
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
-      </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -3978,8 +4193,14 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4067,8 +4288,14 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4156,8 +4383,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4245,8 +4478,14 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4271,11 +4510,11 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -4308,22 +4547,22 @@
         <v>0</v>
       </c>
       <c r="W52" s="3">
+        <v>0</v>
+      </c>
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
         <v>400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>200</v>
       </c>
-      <c r="Z52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
+      <c r="AB52" s="3">
+        <v>0</v>
       </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
@@ -4334,8 +4573,14 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4423,85 +4668,91 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>13900</v>
+      </c>
+      <c r="F54" s="3">
         <v>14400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>5000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>7800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>10200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>10200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>22800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>25500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>36000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>32500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>36500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>43300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>46000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>47700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>49500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>6000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>8100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>9400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>10200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>11400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1100</v>
-      </c>
-      <c r="X54" s="3">
-        <v>400</v>
-      </c>
-      <c r="Y54" s="3">
-        <v>300</v>
       </c>
       <c r="Z54" s="3">
         <v>400</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
+      <c r="AA54" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB54" s="3">
+        <v>400</v>
       </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
@@ -4512,8 +4763,14 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4545,8 +4802,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4578,85 +4837,87 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4100</v>
+        <v>1400</v>
       </c>
       <c r="E57" s="3">
-        <v>3400</v>
+        <v>2300</v>
       </c>
       <c r="F57" s="3">
         <v>4100</v>
       </c>
       <c r="G57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H57" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I57" s="3">
         <v>1300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>4200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>4000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>300</v>
-      </c>
-      <c r="T57" s="3">
-        <v>100</v>
-      </c>
-      <c r="U57" s="3">
-        <v>100</v>
       </c>
       <c r="V57" s="3">
         <v>100</v>
       </c>
       <c r="W57" s="3">
+        <v>100</v>
+      </c>
+      <c r="X57" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y57" s="3">
         <v>1200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>400</v>
       </c>
-      <c r="Y57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
+      <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="3">
+        <v>0</v>
       </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
@@ -4667,8 +4928,14 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4756,8 +5023,14 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4782,23 +5055,23 @@
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>3700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>300</v>
-      </c>
-      <c r="O59" s="3">
-        <v>800</v>
-      </c>
-      <c r="P59" s="3">
-        <v>800</v>
       </c>
       <c r="Q59" s="3">
         <v>800</v>
@@ -4807,19 +5080,19 @@
         <v>800</v>
       </c>
       <c r="S59" s="3">
+        <v>800</v>
+      </c>
+      <c r="T59" s="3">
+        <v>800</v>
+      </c>
+      <c r="U59" s="3">
         <v>200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>600</v>
-      </c>
-      <c r="V59" s="3">
-        <v>700</v>
-      </c>
-      <c r="W59" s="3">
-        <v>800</v>
       </c>
       <c r="X59" s="3">
         <v>700</v>
@@ -4828,14 +5101,14 @@
         <v>800</v>
       </c>
       <c r="Z59" s="3">
+        <v>700</v>
+      </c>
+      <c r="AA59" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB59" s="3">
         <v>600</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4845,86 +5118,92 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F60" s="3">
         <v>5400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>4100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>4900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>4300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>5400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>7700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>2000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>600</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4934,8 +5213,14 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4997,10 +5282,10 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="X61" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="Y61" s="3">
         <v>500</v>
@@ -5009,10 +5294,10 @@
         <v>500</v>
       </c>
       <c r="AA61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AB61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AC61" s="3">
         <v>0</v>
@@ -5023,29 +5308,35 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>700</v>
+      </c>
+      <c r="F62" s="3">
         <v>1900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>2700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>6300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>13700</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5055,11 +5346,11 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
-      <c r="N62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O62" s="3">
         <v>0</v>
@@ -5086,22 +5377,22 @@
         <v>0</v>
       </c>
       <c r="W62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y62" s="3">
         <v>100</v>
       </c>
       <c r="Z62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB62" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="AA62" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB62" s="3">
+        <v>0</v>
       </c>
       <c r="AC62" s="3" t="s">
         <v>3</v>
@@ -5112,8 +5403,14 @@
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,8 +5498,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5290,8 +5593,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5379,86 +5688,92 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F66" s="3">
         <v>7300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>6800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>11200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>18000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>5400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>7700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>2500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>2600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1100</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5468,8 +5783,14 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5501,8 +5822,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5590,8 +5913,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5679,8 +6008,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5742,10 +6077,10 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
-        <v>7100</v>
+        <v>0</v>
       </c>
       <c r="X70" s="3">
-        <v>7100</v>
+        <v>0</v>
       </c>
       <c r="Y70" s="3">
         <v>7100</v>
@@ -5754,10 +6089,10 @@
         <v>7100</v>
       </c>
       <c r="AA70" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="AB70" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="AC70" s="3">
         <v>0</v>
@@ -5768,8 +6103,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5857,86 +6198,92 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-140400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-134800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-129000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-116300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-111300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-110300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-88000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-73300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-63800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-54100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-51000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-43300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-34600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-28700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-22800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-20000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-17400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-14200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-12500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-11500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-9200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-8800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-8600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5946,8 +6293,14 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6035,8 +6388,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6124,8 +6483,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6213,86 +6578,92 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F76" s="3">
         <v>7100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-1800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-3400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-7800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>6700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>20700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>20100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>28300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>30000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>35200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>42000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>44500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>46500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>48600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>4400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>7500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>9100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>9500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>10700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>-8600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>-8400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>-8100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>-7800</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6302,8 +6673,14 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6391,191 +6768,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-12600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-5000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-22200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-14700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-9500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-9700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-3100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-6400</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-5200</v>
       </c>
       <c r="O81" s="3">
         <v>-5900</v>
       </c>
       <c r="P81" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="R81" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-2500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-3200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-1700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-1000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-2300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>-100</v>
       </c>
       <c r="AC81" s="3">
         <v>-200</v>
       </c>
       <c r="AD81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE81" s="3">
         <v>-200</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6607,8 +7002,10 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6633,11 +7030,11 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -6696,8 +7093,14 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6785,8 +7188,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6874,8 +7283,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6963,8 +7378,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7052,8 +7473,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7141,97 +7568,109 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-3200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-3400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-7000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-9400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-9400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-9600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-11600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-3600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-4000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-6700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-3000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-1800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-3100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-2500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-1300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-1000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-100</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-200</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7263,8 +7702,10 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7289,11 +7730,11 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -7352,8 +7793,14 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7441,8 +7888,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,8 +7983,14 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7556,11 +8015,11 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -7619,8 +8078,14 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7652,8 +8117,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7678,11 +8145,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7741,8 +8208,14 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7830,8 +8303,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7919,8 +8398,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8008,35 +8493,41 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F100" s="3">
         <v>11800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>4200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>4400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>8800</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>8600</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
@@ -8053,14 +8544,14 @@
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>46800</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
@@ -8068,37 +8559,43 @@
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>12100</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>500</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
         <v>0</v>
       </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>200</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8123,11 +8620,11 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -8186,93 +8683,105 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F102" s="3">
         <v>8600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-2600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-9400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-1000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-11600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-3600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-4000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-6700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-3000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>43600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-2500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-1400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>11100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-100</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>100</v>
       </c>
-      <c r="AE102" s="3" t="s">
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ANVS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANVS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="92">
   <si>
     <t>ANVS</t>
   </si>
@@ -656,144 +656,148 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -824,8 +828,8 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -887,8 +891,11 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -982,8 +989,11 @@
       <c r="AG9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1077,8 +1087,11 @@
       <c r="AG10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1112,80 +1125,81 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>5000</v>
+        <v>5200</v>
       </c>
       <c r="E12" s="3">
         <v>5000</v>
       </c>
       <c r="F12" s="3">
+        <v>5000</v>
+      </c>
+      <c r="G12" s="3">
         <v>2700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>5800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>8900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>13800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>8300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>7800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>800</v>
       </c>
-      <c r="Z12" s="3">
-        <v>0</v>
-      </c>
       <c r="AA12" s="3">
         <v>0</v>
       </c>
@@ -1193,22 +1207,25 @@
         <v>0</v>
       </c>
       <c r="AC12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="3">
         <v>200</v>
       </c>
-      <c r="AD12" s="3">
-        <v>0</v>
-      </c>
       <c r="AE12" s="3">
         <v>0</v>
       </c>
       <c r="AF12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="3">
         <v>100</v>
       </c>
-      <c r="AG12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,8 +1319,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1334,8 +1354,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1359,23 +1379,23 @@
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>-200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-600</v>
-      </c>
-      <c r="W14" s="3">
-        <v>-200</v>
       </c>
       <c r="X14" s="3">
         <v>-200</v>
       </c>
       <c r="Y14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-700</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1388,8 +1408,8 @@
       <c r="AD14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
@@ -1397,8 +1417,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1492,8 +1515,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,8 +1550,9 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1533,94 +1560,97 @@
         <v>6300</v>
       </c>
       <c r="E17" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F17" s="3">
         <v>6700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4400</v>
-      </c>
-      <c r="G17" s="3">
-        <v>7800</v>
       </c>
       <c r="H17" s="3">
         <v>7800</v>
       </c>
       <c r="I17" s="3">
+        <v>7800</v>
+      </c>
+      <c r="J17" s="3">
         <v>10400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>300</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>200</v>
       </c>
       <c r="AC17" s="3">
         <v>200</v>
       </c>
       <c r="AD17" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE17" s="3">
         <v>100</v>
-      </c>
-      <c r="AE17" s="3">
-        <v>200</v>
       </c>
       <c r="AF17" s="3">
         <v>200</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1628,94 +1658,97 @@
         <v>-6300</v>
       </c>
       <c r="E18" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-6700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4400</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-7800</v>
       </c>
       <c r="H18" s="3">
         <v>-7800</v>
       </c>
       <c r="I18" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="J18" s="3">
         <v>-10400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-14900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-9800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-10000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-6000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-300</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>-200</v>
       </c>
       <c r="AC18" s="3">
         <v>-200</v>
       </c>
       <c r="AD18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-100</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>-200</v>
       </c>
       <c r="AF18" s="3">
         <v>-200</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AH18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,46 +1782,47 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>8400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-6700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>11800</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3">
-        <v>100</v>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N20" s="3">
         <v>100</v>
       </c>
       <c r="O20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -1818,11 +1852,11 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
@@ -1841,44 +1875,47 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-5700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-6000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-12800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-5000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-22300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-14900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-9800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-10000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1939,8 +1976,11 @@
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1971,8 +2011,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2034,103 +2074,109 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-12600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-22200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-14700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>-300</v>
       </c>
       <c r="AA23" s="3">
         <v>-300</v>
       </c>
       <c r="AB23" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AC23" s="3">
         <v>-200</v>
       </c>
       <c r="AD23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE23" s="3">
         <v>-100</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>-200</v>
       </c>
       <c r="AF23" s="3">
         <v>-200</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2161,8 +2207,8 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -2224,8 +2270,11 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2368,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-22200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-14700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-6400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>-300</v>
       </c>
       <c r="AA26" s="3">
         <v>-300</v>
       </c>
       <c r="AB26" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AC26" s="3">
         <v>-200</v>
       </c>
       <c r="AD26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE26" s="3">
         <v>-100</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>-200</v>
       </c>
       <c r="AF26" s="3">
         <v>-200</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AH26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-12600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-22200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-14700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-6400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>-300</v>
       </c>
       <c r="AA27" s="3">
         <v>-300</v>
       </c>
       <c r="AB27" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AC27" s="3">
         <v>-200</v>
       </c>
       <c r="AD27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE27" s="3">
         <v>-100</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>-200</v>
       </c>
       <c r="AF27" s="3">
         <v>-200</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AH27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2662,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2699,8 +2760,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2858,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,46 +2956,49 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-8400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>6700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-11800</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3">
-        <v>-100</v>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N32" s="3">
         <v>-100</v>
       </c>
       <c r="O32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
@@ -2958,11 +3028,11 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>100</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
@@ -2981,106 +3051,112 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-12600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-22200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-14700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-6400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>-300</v>
       </c>
       <c r="AA33" s="3">
         <v>-300</v>
       </c>
       <c r="AB33" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AC33" s="3">
         <v>-200</v>
       </c>
       <c r="AD33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE33" s="3">
         <v>-100</v>
-      </c>
-      <c r="AE33" s="3">
-        <v>-200</v>
       </c>
       <c r="AF33" s="3">
         <v>-200</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AH33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3250,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-12600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-22200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-14700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-6400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>-300</v>
       </c>
       <c r="AA35" s="3">
         <v>-300</v>
       </c>
       <c r="AB35" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AC35" s="3">
         <v>-200</v>
       </c>
       <c r="AD35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE35" s="3">
         <v>-100</v>
-      </c>
-      <c r="AE35" s="3">
-        <v>-200</v>
       </c>
       <c r="AF35" s="3">
         <v>-200</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AH35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3489,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,89 +3525,90 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E41" s="3">
         <v>22200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>15700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>16800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>28400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>32000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>36000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>42700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>45700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>47500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>49200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>11100</v>
       </c>
-      <c r="Y41" s="3">
-        <v>0</v>
-      </c>
       <c r="Z41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA41" s="3">
         <v>100</v>
       </c>
       <c r="AB41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC41" s="3">
         <v>300</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3534,8 +3621,11 @@
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3629,8 +3719,11 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3661,8 +3754,8 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -3685,24 +3778,24 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V43" s="3">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W43" s="3">
         <v>400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>200</v>
       </c>
-      <c r="X43" s="3">
-        <v>0</v>
-      </c>
       <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="3">
         <v>700</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3715,8 +3808,8 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE43" s="3">
-        <v>0</v>
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF43" s="3">
         <v>0</v>
@@ -3724,8 +3817,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3756,8 +3852,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3819,77 +3915,80 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>3900</v>
       </c>
       <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
         <v>3000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>700</v>
-      </c>
-      <c r="H45" s="3">
-        <v>4400</v>
       </c>
       <c r="I45" s="3">
         <v>4400</v>
       </c>
       <c r="J45" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K45" s="3">
         <v>3700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>500</v>
-      </c>
-      <c r="O45" s="3">
-        <v>600</v>
       </c>
       <c r="P45" s="3">
         <v>600</v>
       </c>
       <c r="Q45" s="3">
+        <v>600</v>
+      </c>
+      <c r="R45" s="3">
         <v>300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>400</v>
       </c>
-      <c r="U45" s="3">
-        <v>0</v>
-      </c>
       <c r="V45" s="3">
+        <v>0</v>
+      </c>
+      <c r="W45" s="3">
         <v>100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>300</v>
       </c>
-      <c r="Y45" s="3">
-        <v>0</v>
-      </c>
       <c r="Z45" s="3">
         <v>0</v>
       </c>
@@ -3897,11 +3996,11 @@
         <v>0</v>
       </c>
       <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="3">
         <v>100</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3914,89 +4013,92 @@
       <c r="AG45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E46" s="3">
         <v>26700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>14400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7800</v>
-      </c>
-      <c r="I46" s="3">
-        <v>10200</v>
       </c>
       <c r="J46" s="3">
         <v>10200</v>
       </c>
       <c r="K46" s="3">
+        <v>10200</v>
+      </c>
+      <c r="L46" s="3">
         <v>22800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>25500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>36000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>32500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>36500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>43300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>46000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>47700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>49500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>8100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>9400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>10200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>11400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>700</v>
-      </c>
-      <c r="Z46" s="3">
-        <v>100</v>
       </c>
       <c r="AA46" s="3">
         <v>100</v>
       </c>
       <c r="AB46" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC46" s="3">
         <v>400</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4009,8 +4111,11 @@
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4041,8 +4146,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4104,8 +4209,11 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4136,8 +4244,8 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -4199,8 +4307,11 @@
       <c r="AG48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4294,8 +4405,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4503,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,8 +4601,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4516,8 +4636,8 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -4553,19 +4673,19 @@
         <v>0</v>
       </c>
       <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3">
         <v>400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>200</v>
       </c>
-      <c r="AB52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC52" s="3" t="s">
-        <v>3</v>
+      <c r="AC52" s="3">
+        <v>0</v>
       </c>
       <c r="AD52" s="3" t="s">
         <v>3</v>
@@ -4579,8 +4699,11 @@
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,89 +4797,92 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E54" s="3">
         <v>26700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>14400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7800</v>
-      </c>
-      <c r="I54" s="3">
-        <v>10200</v>
       </c>
       <c r="J54" s="3">
         <v>10200</v>
       </c>
       <c r="K54" s="3">
+        <v>10200</v>
+      </c>
+      <c r="L54" s="3">
         <v>22800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>25500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>36000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>32500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>36500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>43300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>46000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>47700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>49500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>8100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>9400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>10200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>11400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>400</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4769,8 +4895,11 @@
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4933,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,67 +4969,68 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1800</v>
-      </c>
-      <c r="O57" s="3">
-        <v>900</v>
       </c>
       <c r="P57" s="3">
         <v>900</v>
       </c>
       <c r="Q57" s="3">
+        <v>900</v>
+      </c>
+      <c r="R57" s="3">
         <v>700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>300</v>
-      </c>
-      <c r="V57" s="3">
-        <v>100</v>
       </c>
       <c r="W57" s="3">
         <v>100</v>
@@ -4908,19 +5039,19 @@
         <v>100</v>
       </c>
       <c r="Y57" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z57" s="3">
         <v>1200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>400</v>
       </c>
-      <c r="AA57" s="3">
-        <v>0</v>
-      </c>
       <c r="AB57" s="3">
         <v>0</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>3</v>
+      <c r="AC57" s="3">
+        <v>0</v>
       </c>
       <c r="AD57" s="3" t="s">
         <v>3</v>
@@ -4934,8 +5065,11 @@
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5029,8 +5163,11 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5061,20 +5198,20 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>3700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>300</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>800</v>
       </c>
       <c r="R59" s="3">
         <v>800</v>
@@ -5086,32 +5223,32 @@
         <v>800</v>
       </c>
       <c r="U59" s="3">
+        <v>800</v>
+      </c>
+      <c r="V59" s="3">
         <v>200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>600</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5124,89 +5261,92 @@
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E60" s="3">
         <v>2500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2500</v>
-      </c>
-      <c r="O60" s="3">
-        <v>1300</v>
       </c>
       <c r="P60" s="3">
         <v>1300</v>
       </c>
       <c r="Q60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="R60" s="3">
         <v>1500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>300</v>
-      </c>
-      <c r="W60" s="3">
-        <v>700</v>
       </c>
       <c r="X60" s="3">
         <v>700</v>
       </c>
       <c r="Y60" s="3">
+        <v>700</v>
+      </c>
+      <c r="Z60" s="3">
         <v>2000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>600</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5219,8 +5359,11 @@
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5288,7 +5431,7 @@
         <v>0</v>
       </c>
       <c r="Y61" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="Z61" s="3">
         <v>500</v>
@@ -5300,7 +5443,7 @@
         <v>500</v>
       </c>
       <c r="AC61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD61" s="3">
         <v>0</v>
@@ -5314,32 +5457,35 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>300</v>
+      </c>
+      <c r="E62" s="3">
         <v>200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13700</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5352,8 +5498,8 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -5383,7 +5529,7 @@
         <v>0</v>
       </c>
       <c r="Y62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z62" s="3">
         <v>100</v>
@@ -5392,10 +5538,10 @@
         <v>100</v>
       </c>
       <c r="AB62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC62" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="AC62" s="3">
+        <v>0</v>
       </c>
       <c r="AD62" s="3" t="s">
         <v>3</v>
@@ -5409,8 +5555,11 @@
       <c r="AG62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5653,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5751,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,89 +5849,92 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E66" s="3">
         <v>2700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>18000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2500</v>
-      </c>
-      <c r="O66" s="3">
-        <v>1300</v>
       </c>
       <c r="P66" s="3">
         <v>1300</v>
       </c>
       <c r="Q66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="R66" s="3">
         <v>1500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>300</v>
-      </c>
-      <c r="W66" s="3">
-        <v>700</v>
       </c>
       <c r="X66" s="3">
         <v>700</v>
       </c>
       <c r="Y66" s="3">
+        <v>700</v>
+      </c>
+      <c r="Z66" s="3">
         <v>2600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1100</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5789,8 +5947,11 @@
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5985,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6081,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6179,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6083,7 +6251,7 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
-        <v>7100</v>
+        <v>0</v>
       </c>
       <c r="Z70" s="3">
         <v>7100</v>
@@ -6095,7 +6263,7 @@
         <v>7100</v>
       </c>
       <c r="AC70" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="AD70" s="3">
         <v>0</v>
@@ -6109,8 +6277,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,89 +6375,92 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-146600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-140400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-134800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-129000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-116300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-111300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-110300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-88000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-73300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-63800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-54100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-51000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-43300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-34600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-28700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-22800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-20000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-17400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-14200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-12500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-11500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-9200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-8800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-8600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-8300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6299,8 +6473,11 @@
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6571,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6669,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,89 +6767,92 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E76" s="3">
         <v>24100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-3400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-7800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>28300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>30000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>35200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>42000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>44500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>46500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>48600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-8600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-8400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-8100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-7800</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6679,8 +6865,11 @@
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +6963,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-12600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-22200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-14700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-6400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>-300</v>
       </c>
       <c r="AA81" s="3">
         <v>-300</v>
       </c>
       <c r="AB81" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AC81" s="3">
         <v>-200</v>
       </c>
       <c r="AD81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AE81" s="3">
         <v>-100</v>
-      </c>
-      <c r="AE81" s="3">
-        <v>-200</v>
       </c>
       <c r="AF81" s="3">
         <v>-200</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AH81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,8 +7202,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7036,8 +7235,8 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -7099,8 +7298,11 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7396,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7494,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7592,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7690,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +7788,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-8100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-8300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7000</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-9400</v>
       </c>
       <c r="J89" s="3">
         <v>-9400</v>
       </c>
       <c r="K89" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="L89" s="3">
         <v>-9600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-11600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-6700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-100</v>
       </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
       <c r="AA89" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="AB89" s="3">
         <v>-200</v>
       </c>
       <c r="AC89" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AD89" s="3">
         <v>-100</v>
       </c>
       <c r="AE89" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="AF89" s="3">
         <v>-200</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AH89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,8 +7924,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7736,8 +7957,8 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -7799,8 +8020,11 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8118,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,8 +8216,11 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8021,8 +8251,8 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -8084,8 +8314,11 @@
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8352,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8151,8 +8385,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -8214,8 +8448,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8546,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8644,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,38 +8742,41 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>19800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>11800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>4400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>8800</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>8600</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
@@ -8550,11 +8796,11 @@
         <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>46800</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
@@ -8565,23 +8811,23 @@
         <v>0</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>12100</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>500</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
         <v>0</v>
       </c>
@@ -8589,13 +8835,16 @@
         <v>0</v>
       </c>
       <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>200</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8626,8 +8875,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -8689,99 +8938,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E102" s="3">
         <v>11700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>8600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-9400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-11600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3000</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>-1800</v>
       </c>
       <c r="R102" s="3">
         <v>-1800</v>
       </c>
       <c r="S102" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="T102" s="3">
         <v>43600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>11100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-100</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>300</v>
-      </c>
-      <c r="AC102" s="3">
-        <v>-100</v>
       </c>
       <c r="AD102" s="3">
         <v>-100</v>
       </c>
       <c r="AE102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>100</v>
       </c>
-      <c r="AG102" s="3" t="s">
+      <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ANVS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANVS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="92">
   <si>
     <t>ANVS</t>
   </si>
@@ -656,152 +656,155 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2" t="s">
+      <c r="AJ7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -838,8 +841,8 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -901,8 +904,11 @@
       <c r="AI8" s="3">
         <v>0</v>
       </c>
+      <c r="AJ8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1002,8 +1008,11 @@
       <c r="AI9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1103,8 +1112,11 @@
       <c r="AI10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1140,86 +1152,87 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E12" s="3">
         <v>6300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>5200</v>
-      </c>
-      <c r="F12" s="3">
-        <v>5000</v>
       </c>
       <c r="G12" s="3">
         <v>5000</v>
       </c>
       <c r="H12" s="3">
+        <v>5000</v>
+      </c>
+      <c r="I12" s="3">
         <v>2700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>8900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>13800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>8300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>7800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>4100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>4000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>800</v>
       </c>
-      <c r="AB12" s="3">
-        <v>0</v>
-      </c>
       <c r="AC12" s="3">
         <v>0</v>
       </c>
@@ -1227,22 +1240,25 @@
         <v>0</v>
       </c>
       <c r="AE12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="3">
         <v>200</v>
       </c>
-      <c r="AF12" s="3">
-        <v>0</v>
-      </c>
       <c r="AG12" s="3">
         <v>0</v>
       </c>
       <c r="AH12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="3">
         <v>100</v>
       </c>
-      <c r="AI12" s="3" t="s">
+      <c r="AJ12" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1342,8 +1358,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1380,8 +1399,8 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1405,23 +1424,23 @@
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>-200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-600</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>-200</v>
       </c>
       <c r="Z14" s="3">
         <v>-200</v>
       </c>
       <c r="AA14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AB14" s="3">
         <v>-700</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1434,8 +1453,8 @@
       <c r="AF14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
@@ -1443,8 +1462,11 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1544,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1578,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E17" s="3">
         <v>7400</v>
-      </c>
-      <c r="E17" s="3">
-        <v>6300</v>
       </c>
       <c r="F17" s="3">
         <v>6300</v>
       </c>
       <c r="G17" s="3">
+        <v>6300</v>
+      </c>
+      <c r="H17" s="3">
         <v>6700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4400</v>
-      </c>
-      <c r="I17" s="3">
-        <v>7800</v>
       </c>
       <c r="J17" s="3">
         <v>7800</v>
       </c>
       <c r="K17" s="3">
+        <v>7800</v>
+      </c>
+      <c r="L17" s="3">
         <v>10400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>300</v>
-      </c>
-      <c r="AD17" s="3">
-        <v>200</v>
       </c>
       <c r="AE17" s="3">
         <v>200</v>
       </c>
       <c r="AF17" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG17" s="3">
         <v>100</v>
-      </c>
-      <c r="AG17" s="3">
-        <v>200</v>
       </c>
       <c r="AH17" s="3">
         <v>200</v>
       </c>
-      <c r="AI17" s="3" t="s">
+      <c r="AI17" s="3">
+        <v>200</v>
+      </c>
+      <c r="AJ17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-7400</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-6300</v>
       </c>
       <c r="F18" s="3">
         <v>-6300</v>
       </c>
       <c r="G18" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="H18" s="3">
         <v>-6700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-4400</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-7800</v>
       </c>
       <c r="J18" s="3">
         <v>-7800</v>
       </c>
       <c r="K18" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="L18" s="3">
         <v>-10400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-14900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-9800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-10000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-6000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-300</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>-200</v>
       </c>
       <c r="AE18" s="3">
         <v>-200</v>
       </c>
       <c r="AF18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG18" s="3">
         <v>-100</v>
-      </c>
-      <c r="AG18" s="3">
-        <v>-200</v>
       </c>
       <c r="AH18" s="3">
         <v>-200</v>
       </c>
-      <c r="AI18" s="3" t="s">
+      <c r="AI18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AJ18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1817,52 +1849,53 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>8400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-6700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>11800</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3">
-        <v>100</v>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P20" s="3">
         <v>100</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -1892,11 +1925,11 @@
         <v>0</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-100</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
@@ -1915,50 +1948,53 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-      <c r="AI20" s="3" t="s">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-7400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-6400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-5700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-6000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-12800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-5000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-22300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-14900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-9800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-10000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -2019,8 +2055,11 @@
       <c r="AI21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2057,8 +2096,8 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2120,109 +2159,115 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-12600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-22200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-14700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-200</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>-300</v>
       </c>
       <c r="AC23" s="3">
         <v>-300</v>
       </c>
       <c r="AD23" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AE23" s="3">
         <v>-200</v>
       </c>
       <c r="AF23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG23" s="3">
         <v>-100</v>
-      </c>
-      <c r="AG23" s="3">
-        <v>-200</v>
       </c>
       <c r="AH23" s="3">
         <v>-200</v>
       </c>
-      <c r="AI23" s="3" t="s">
+      <c r="AI23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AJ23" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2259,8 +2304,8 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -2322,8 +2367,11 @@
       <c r="AI24" s="3">
         <v>0</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2423,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-7300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-12600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-22200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-14700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-5900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-200</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>-300</v>
       </c>
       <c r="AC26" s="3">
         <v>-300</v>
       </c>
       <c r="AD26" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AE26" s="3">
         <v>-200</v>
       </c>
       <c r="AF26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG26" s="3">
         <v>-100</v>
-      </c>
-      <c r="AG26" s="3">
-        <v>-200</v>
       </c>
       <c r="AH26" s="3">
         <v>-200</v>
       </c>
-      <c r="AI26" s="3" t="s">
+      <c r="AI26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AJ26" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-7300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-12600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-22200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-14700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-5900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-200</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>-300</v>
       </c>
       <c r="AC27" s="3">
         <v>-300</v>
       </c>
       <c r="AD27" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AE27" s="3">
         <v>-200</v>
       </c>
       <c r="AF27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG27" s="3">
         <v>-100</v>
-      </c>
-      <c r="AG27" s="3">
-        <v>-200</v>
       </c>
       <c r="AH27" s="3">
         <v>-200</v>
       </c>
-      <c r="AI27" s="3" t="s">
+      <c r="AI27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AJ27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2726,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2827,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2928,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3029,52 +3095,55 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-8400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>6700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-11800</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3">
-        <v>-100</v>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P32" s="3">
         <v>-100</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -3104,11 +3173,11 @@
         <v>0</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>100</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
@@ -3127,112 +3196,118 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-      <c r="AI32" s="3" t="s">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-7300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-12600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-22200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-14700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-200</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>-300</v>
       </c>
       <c r="AC33" s="3">
         <v>-300</v>
       </c>
       <c r="AD33" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AE33" s="3">
         <v>-200</v>
       </c>
       <c r="AF33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG33" s="3">
         <v>-100</v>
-      </c>
-      <c r="AG33" s="3">
-        <v>-200</v>
       </c>
       <c r="AH33" s="3">
         <v>-200</v>
       </c>
-      <c r="AI33" s="3" t="s">
+      <c r="AI33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AJ33" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3332,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-7300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-12600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-22200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-14700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-200</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>-300</v>
       </c>
       <c r="AC35" s="3">
         <v>-300</v>
       </c>
       <c r="AD35" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AE35" s="3">
         <v>-200</v>
       </c>
       <c r="AF35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG35" s="3">
         <v>-100</v>
-      </c>
-      <c r="AG35" s="3">
-        <v>-200</v>
       </c>
       <c r="AH35" s="3">
         <v>-200</v>
       </c>
-      <c r="AI35" s="3" t="s">
+      <c r="AI35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AJ35" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2" t="s">
+      <c r="AJ38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3576,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3613,95 +3698,96 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E41" s="3">
         <v>15300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>17100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>22200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>15700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>16800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>28400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>32000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>36000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>42700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>45700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>47500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>49200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>8100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>8800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>11100</v>
       </c>
-      <c r="AA41" s="3">
-        <v>0</v>
-      </c>
       <c r="AB41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC41" s="3">
         <v>100</v>
       </c>
       <c r="AD41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE41" s="3">
         <v>300</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3714,8 +3800,11 @@
       <c r="AI41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3815,8 +3904,11 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3853,8 +3945,8 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -3877,24 +3969,24 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X43" s="3">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y43" s="3">
         <v>400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>200</v>
       </c>
-      <c r="Z43" s="3">
-        <v>0</v>
-      </c>
       <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="3">
         <v>700</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3907,8 +3999,8 @@
       <c r="AF43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG43" s="3">
-        <v>0</v>
+      <c r="AG43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH43" s="3">
         <v>0</v>
@@ -3916,8 +4008,11 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3954,8 +4049,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4017,83 +4112,86 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
         <v>3900</v>
       </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
       <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3">
         <v>3000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>700</v>
-      </c>
-      <c r="J45" s="3">
-        <v>4400</v>
       </c>
       <c r="K45" s="3">
         <v>4400</v>
       </c>
       <c r="L45" s="3">
+        <v>4400</v>
+      </c>
+      <c r="M45" s="3">
         <v>3700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>500</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>600</v>
       </c>
       <c r="R45" s="3">
         <v>600</v>
       </c>
       <c r="S45" s="3">
+        <v>600</v>
+      </c>
+      <c r="T45" s="3">
         <v>300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>400</v>
       </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
       <c r="X45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
         <v>100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>300</v>
       </c>
-      <c r="AA45" s="3">
-        <v>0</v>
-      </c>
       <c r="AB45" s="3">
         <v>0</v>
       </c>
@@ -4101,11 +4199,11 @@
         <v>0</v>
       </c>
       <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="3">
         <v>100</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4118,95 +4216,98 @@
       <c r="AI45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E46" s="3">
         <v>17200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>21500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>26700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7800</v>
-      </c>
-      <c r="K46" s="3">
-        <v>10200</v>
       </c>
       <c r="L46" s="3">
         <v>10200</v>
       </c>
       <c r="M46" s="3">
+        <v>10200</v>
+      </c>
+      <c r="N46" s="3">
         <v>22800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>25500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>36000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>32500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>36500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>43300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>46000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>47700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>49500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>8100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>9400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>10200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>11400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>700</v>
-      </c>
-      <c r="AB46" s="3">
-        <v>100</v>
       </c>
       <c r="AC46" s="3">
         <v>100</v>
       </c>
       <c r="AD46" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE46" s="3">
         <v>400</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4219,8 +4320,11 @@
       <c r="AI46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4257,8 +4361,8 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4320,8 +4424,11 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4358,8 +4465,8 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
+      <c r="O48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
@@ -4421,8 +4528,11 @@
       <c r="AI48" s="3">
         <v>0</v>
       </c>
+      <c r="AJ48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4522,8 +4632,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4623,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4724,8 +4840,11 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4762,8 +4881,8 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -4799,19 +4918,19 @@
         <v>0</v>
       </c>
       <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="3">
         <v>400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>200</v>
       </c>
-      <c r="AD52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE52" s="3" t="s">
-        <v>3</v>
+      <c r="AE52" s="3">
+        <v>0</v>
       </c>
       <c r="AF52" s="3" t="s">
         <v>3</v>
@@ -4825,8 +4944,11 @@
       <c r="AI52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4926,95 +5048,98 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E54" s="3">
         <v>17200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>21500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>26700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7800</v>
-      </c>
-      <c r="K54" s="3">
-        <v>10200</v>
       </c>
       <c r="L54" s="3">
         <v>10200</v>
       </c>
       <c r="M54" s="3">
+        <v>10200</v>
+      </c>
+      <c r="N54" s="3">
         <v>22800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>25500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>36000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>32500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>36500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>43300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>46000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>47700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>49500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>8100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>9400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>10200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>11400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>400</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5027,8 +5152,11 @@
       <c r="AI54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5064,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5101,73 +5230,74 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E57" s="3">
         <v>2100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1800</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>900</v>
       </c>
       <c r="R57" s="3">
         <v>900</v>
       </c>
       <c r="S57" s="3">
+        <v>900</v>
+      </c>
+      <c r="T57" s="3">
         <v>700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>300</v>
-      </c>
-      <c r="X57" s="3">
-        <v>100</v>
       </c>
       <c r="Y57" s="3">
         <v>100</v>
@@ -5176,19 +5306,19 @@
         <v>100</v>
       </c>
       <c r="AA57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB57" s="3">
         <v>1200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>400</v>
       </c>
-      <c r="AC57" s="3">
-        <v>0</v>
-      </c>
       <c r="AD57" s="3">
         <v>0</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>3</v>
+      <c r="AE57" s="3">
+        <v>0</v>
       </c>
       <c r="AF57" s="3" t="s">
         <v>3</v>
@@ -5202,8 +5332,11 @@
       <c r="AI57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5303,8 +5436,11 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5341,20 +5477,20 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3">
         <v>3700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>300</v>
-      </c>
-      <c r="S59" s="3">
-        <v>800</v>
       </c>
       <c r="T59" s="3">
         <v>800</v>
@@ -5366,32 +5502,32 @@
         <v>800</v>
       </c>
       <c r="W59" s="3">
+        <v>800</v>
+      </c>
+      <c r="X59" s="3">
         <v>200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>600</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5404,95 +5540,98 @@
       <c r="AI59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E60" s="3">
         <v>3700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2500</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>1300</v>
       </c>
       <c r="R60" s="3">
         <v>1300</v>
       </c>
       <c r="S60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="T60" s="3">
         <v>1500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>300</v>
-      </c>
-      <c r="Y60" s="3">
-        <v>700</v>
       </c>
       <c r="Z60" s="3">
         <v>700</v>
       </c>
       <c r="AA60" s="3">
+        <v>700</v>
+      </c>
+      <c r="AB60" s="3">
         <v>2000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>600</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5505,8 +5644,11 @@
       <c r="AI60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5580,7 +5722,7 @@
         <v>0</v>
       </c>
       <c r="AA61" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AB61" s="3">
         <v>500</v>
@@ -5592,7 +5734,7 @@
         <v>500</v>
       </c>
       <c r="AE61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AF61" s="3">
         <v>0</v>
@@ -5606,38 +5748,41 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="E62" s="3">
         <v>300</v>
       </c>
       <c r="F62" s="3">
+        <v>300</v>
+      </c>
+      <c r="G62" s="3">
         <v>200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13700</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5650,8 +5795,8 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
@@ -5681,7 +5826,7 @@
         <v>0</v>
       </c>
       <c r="AA62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB62" s="3">
         <v>100</v>
@@ -5690,10 +5835,10 @@
         <v>100</v>
       </c>
       <c r="AD62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE62" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="AE62" s="3">
+        <v>0</v>
       </c>
       <c r="AF62" s="3" t="s">
         <v>3</v>
@@ -5707,8 +5852,11 @@
       <c r="AI62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5808,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5909,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6010,95 +6164,98 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E66" s="3">
         <v>4000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>18000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2500</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>1300</v>
       </c>
       <c r="R66" s="3">
         <v>1300</v>
       </c>
       <c r="S66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="T66" s="3">
         <v>1500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>300</v>
-      </c>
-      <c r="Y66" s="3">
-        <v>700</v>
       </c>
       <c r="Z66" s="3">
         <v>700</v>
       </c>
       <c r="AA66" s="3">
+        <v>700</v>
+      </c>
+      <c r="AB66" s="3">
         <v>2600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1100</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6111,8 +6268,11 @@
       <c r="AI66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6148,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6249,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6350,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6425,7 +6592,7 @@
         <v>0</v>
       </c>
       <c r="AA70" s="3">
-        <v>7100</v>
+        <v>0</v>
       </c>
       <c r="AB70" s="3">
         <v>7100</v>
@@ -6437,7 +6604,7 @@
         <v>7100</v>
       </c>
       <c r="AE70" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="AF70" s="3">
         <v>0</v>
@@ -6451,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6552,95 +6722,98 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-163700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-153900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-146600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-140400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-134800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-129000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-116300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-111300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-110300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-88000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-73300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-63800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-54100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-51000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-43300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-34600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-28700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-22800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-20000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-17400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-14200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-12500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-11500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-9200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-8800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-8600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-8300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-8000</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6653,8 +6826,11 @@
       <c r="AI72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6754,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6855,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6956,95 +7138,98 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E76" s="3">
         <v>13200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>24100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-3400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-7800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>28300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>30000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>35200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>42000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>44500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>46500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>48600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>9100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>10700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-8600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-8400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-8100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-7800</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7057,8 +7242,11 @@
       <c r="AI76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7158,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2" t="s">
+      <c r="AJ80" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-7300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-12600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-22200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-14700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-200</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>-300</v>
       </c>
       <c r="AC81" s="3">
         <v>-300</v>
       </c>
       <c r="AD81" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AE81" s="3">
         <v>-200</v>
       </c>
       <c r="AF81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG81" s="3">
         <v>-100</v>
-      </c>
-      <c r="AG81" s="3">
-        <v>-200</v>
       </c>
       <c r="AH81" s="3">
         <v>-200</v>
       </c>
-      <c r="AI81" s="3" t="s">
+      <c r="AI81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AJ81" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7402,8 +7599,9 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7440,8 +7638,8 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
@@ -7503,8 +7701,11 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7604,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7705,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7806,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7907,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8008,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-8100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-8300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7000</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-9400</v>
       </c>
       <c r="L89" s="3">
         <v>-9400</v>
       </c>
       <c r="M89" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="N89" s="3">
         <v>-9600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-11600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-6700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-3000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-3100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-100</v>
       </c>
-      <c r="AB89" s="3">
-        <v>0</v>
-      </c>
       <c r="AC89" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="AD89" s="3">
         <v>-200</v>
       </c>
       <c r="AE89" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AF89" s="3">
         <v>-100</v>
       </c>
       <c r="AG89" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="AH89" s="3">
         <v>-200</v>
       </c>
-      <c r="AI89" s="3" t="s">
+      <c r="AI89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AJ89" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8146,8 +8365,9 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8184,8 +8404,8 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -8247,8 +8467,11 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8348,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8449,8 +8675,11 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8487,8 +8716,8 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
@@ -8550,8 +8779,11 @@
       <c r="AI94" s="3">
         <v>0</v>
       </c>
+      <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8587,8 +8819,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8625,8 +8858,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -8688,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8789,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8890,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8991,44 +9233,47 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E100" s="3">
         <v>1600</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>19800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>6200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>11800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>4200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>8800</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>8600</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
@@ -9048,11 +9293,11 @@
         <v>0</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>46800</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
@@ -9063,23 +9308,23 @@
         <v>0</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>12100</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
         <v>0</v>
       </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>500</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
       <c r="AF100" s="3">
         <v>0</v>
       </c>
@@ -9087,13 +9332,16 @@
         <v>0</v>
       </c>
       <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
         <v>200</v>
       </c>
-      <c r="AI100" s="3" t="s">
+      <c r="AJ100" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9130,8 +9378,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -9193,105 +9441,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>11700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>8600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-11600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3000</v>
-      </c>
-      <c r="S102" s="3">
-        <v>-1800</v>
       </c>
       <c r="T102" s="3">
         <v>-1800</v>
       </c>
       <c r="U102" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="V102" s="3">
         <v>43600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>11100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-100</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
-      </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>300</v>
-      </c>
-      <c r="AE102" s="3">
-        <v>-100</v>
       </c>
       <c r="AF102" s="3">
         <v>-100</v>
       </c>
       <c r="AG102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH102" s="3">
         <v>-200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>100</v>
       </c>
-      <c r="AI102" s="3" t="s">
+      <c r="AJ102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
